--- a/data/trans_dic/P17A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P17A-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 20,8</t>
+          <t>13,43; 20,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 22,24</t>
+          <t>14,16; 22,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 28,6</t>
+          <t>19,85; 28,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 27,73</t>
+          <t>20,3; 27,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 29,73</t>
+          <t>19,59; 29,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,02; 31,42</t>
+          <t>20,48; 31,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,07; 32,7</t>
+          <t>23,13; 32,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,4</t>
+          <t>21,83; 27,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,54</t>
+          <t>17,15; 22,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,37</t>
+          <t>17,94; 24,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 28,89</t>
+          <t>22,37; 28,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,26; 26,57</t>
+          <t>21,67; 26,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 20,95</t>
+          <t>13,1; 21,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,11; 27,57</t>
+          <t>18,68; 27,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 30,13</t>
+          <t>20,63; 29,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 24,48</t>
+          <t>16,69; 24,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 31,16</t>
+          <t>21,96; 31,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,76; 34,09</t>
+          <t>23,66; 34,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,26; 30,47</t>
+          <t>21,38; 30,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 27,32</t>
+          <t>20,21; 27,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,03; 25,06</t>
+          <t>18,76; 24,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 29,04</t>
+          <t>22,29; 29,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,86; 28,51</t>
+          <t>22,36; 28,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 24,34</t>
+          <t>19,47; 24,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 25,02</t>
+          <t>18,39; 25,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,55; 28,85</t>
+          <t>21,48; 28,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,99; 34,35</t>
+          <t>25,99; 34,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 21,5</t>
+          <t>16,77; 24,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 43,51</t>
+          <t>27,88; 42,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,43; 41,78</t>
+          <t>30,29; 42,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,48; 46,38</t>
+          <t>30,58; 46,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,3; 35,2</t>
+          <t>23,2; 35,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,78; 28,28</t>
+          <t>22,05; 28,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,96; 31,11</t>
+          <t>24,92; 31,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,92; 35,24</t>
+          <t>28,18; 35,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 23,53</t>
+          <t>19,79; 26,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,08; 25,96</t>
+          <t>21,21; 25,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,43; 28,69</t>
+          <t>23,59; 28,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 28,13</t>
+          <t>22,83; 27,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,99</t>
+          <t>17,89; 23,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 34,87</t>
+          <t>27,37; 34,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,26; 36,19</t>
+          <t>29,21; 36,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,4; 35,76</t>
+          <t>29,58; 35,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 25,38</t>
+          <t>22,46; 27,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,33; 28,27</t>
+          <t>24,48; 28,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,49; 30,84</t>
+          <t>26,61; 30,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,5; 30,88</t>
+          <t>26,33; 30,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,34</t>
+          <t>20,75; 24,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,49; 28,59</t>
+          <t>19,56; 28,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,94; 25,35</t>
+          <t>17,78; 24,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 30,56</t>
+          <t>23,1; 30,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 22,31</t>
+          <t>14,1; 20,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,09</t>
+          <t>31,36; 39,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,22; 40,47</t>
+          <t>32,96; 39,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 39,71</t>
+          <t>32,83; 40,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,68; 50,77</t>
+          <t>23,59; 28,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,39; 33,37</t>
+          <t>27,83; 33,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,91; 33,4</t>
+          <t>27,81; 33,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,48; 34,7</t>
+          <t>29,55; 34,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,31; 38,94</t>
+          <t>20,38; 24,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,03</t>
+          <t>5,81; 12,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,53; 19,66</t>
+          <t>10,39; 18,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 19,84</t>
+          <t>11,6; 19,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 19,55</t>
+          <t>4,77; 16,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,01; 34,11</t>
+          <t>28,89; 34,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,61; 35,22</t>
+          <t>29,58; 35,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,02; 36,9</t>
+          <t>31,22; 37,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,13; 25,52</t>
+          <t>20,77; 26,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,78; 29,16</t>
+          <t>24,88; 29,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,32; 31,29</t>
+          <t>26,34; 31,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,45; 32,87</t>
+          <t>27,71; 32,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,65</t>
+          <t>17,83; 22,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,74; 21,36</t>
+          <t>18,71; 21,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 24,32</t>
+          <t>21,29; 24,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,64; 26,67</t>
+          <t>23,9; 26,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 20,45</t>
+          <t>18,31; 21,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,56; 32,76</t>
+          <t>29,45; 32,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,08; 34,37</t>
+          <t>31,09; 34,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,21; 34,41</t>
+          <t>31,18; 34,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,01</t>
+          <t>23,64; 26,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,52; 26,78</t>
+          <t>24,61; 26,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,7; 28,98</t>
+          <t>26,68; 28,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,04; 30,26</t>
+          <t>28,12; 30,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,25</t>
+          <t>21,42; 23,34</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63510; 98566</t>
+          <t>63649; 97189</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62849; 97041</t>
+          <t>61762; 96574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85041; 122722</t>
+          <t>85158; 121156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100629; 140094</t>
+          <t>111767; 152270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>61438; 91168</t>
+          <t>60070; 91571</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65329; 97673</t>
+          <t>63677; 96904</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80065; 113484</t>
+          <t>80259; 113857</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93052; 122587</t>
+          <t>106644; 136426</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132981; 175899</t>
+          <t>133872; 178517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133389; 182104</t>
+          <t>134077; 183473</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174686; 224196</t>
+          <t>173615; 224330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>202560; 253160</t>
+          <t>225108; 277666</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50017; 76877</t>
+          <t>48074; 78401</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79650; 114922</t>
+          <t>77853; 115717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78599; 113676</t>
+          <t>77814; 110864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75882; 110686</t>
+          <t>80654; 117967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81646; 115865</t>
+          <t>81668; 116488</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80103; 114935</t>
+          <t>79771; 115059</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79137; 113434</t>
+          <t>79592; 113851</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76592; 104534</t>
+          <t>85524; 114256</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140585; 185117</t>
+          <t>138628; 181380</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168401; 218921</t>
+          <t>168012; 219781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163847; 213656</t>
+          <t>167581; 214471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>159133; 203209</t>
+          <t>176434; 221284</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97590; 135731</t>
+          <t>99737; 138103</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135192; 181032</t>
+          <t>134762; 179970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135670; 179256</t>
+          <t>135620; 179171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31621; 143704</t>
+          <t>79071; 113622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47422; 73010</t>
+          <t>46780; 70976</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76262; 108271</t>
+          <t>78498; 109414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50631; 77043</t>
+          <t>50799; 77644</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38795; 58608</t>
+          <t>43395; 65672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154692; 200861</t>
+          <t>156570; 200989</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221317; 275771</t>
+          <t>220949; 277612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192087; 242443</t>
+          <t>193867; 243582</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51565; 196454</t>
+          <t>130354; 172268</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>407683</t>
+          <t>447698</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>260602; 320950</t>
+          <t>262305; 318512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>270075; 330789</t>
+          <t>271921; 332817</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265513; 323399</t>
+          <t>262496; 321631</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190311; 248137</t>
+          <t>202375; 262867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>197707; 248368</t>
+          <t>194967; 246159</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>224068; 277117</t>
+          <t>223703; 276964</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>242768; 295341</t>
+          <t>244300; 296501</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102213; 247975</t>
+          <t>193161; 238194</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474176; 550863</t>
+          <t>477076; 553248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>508176; 591796</t>
+          <t>510478; 592945</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>523592; 609972</t>
+          <t>520235; 602262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>288242; 469469</t>
+          <t>413202; 480868</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>357686</t>
+          <t>314091</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>68335; 100241</t>
+          <t>68567; 100866</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91425; 129195</t>
+          <t>90617; 126061</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143094; 189658</t>
+          <t>143377; 188762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73153; 105804</t>
+          <t>79934; 117504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>176043; 222314</t>
+          <t>178348; 224702</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>252649; 307801</t>
+          <t>250708; 303224</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242507; 293131</t>
+          <t>242394; 298465</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>207531; 426867</t>
+          <t>195924; 237649</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251842; 306806</t>
+          <t>255824; 309324</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>354502; 424238</t>
+          <t>353186; 419310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>400652; 471498</t>
+          <t>401593; 470082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>293417; 512050</t>
+          <t>284855; 343944</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17339; 35761</t>
+          <t>17268; 36431</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27913; 52093</t>
+          <t>27541; 50184</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33806; 56958</t>
+          <t>33323; 57366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11113; 47027</t>
+          <t>11323; 39373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>362273; 425943</t>
+          <t>360817; 426691</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>327353; 389374</t>
+          <t>327008; 389848</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>335660; 399305</t>
+          <t>337775; 403249</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>153085; 194038</t>
+          <t>174860; 221973</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>383075; 450789</t>
+          <t>384684; 453144</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>360807; 428905</t>
+          <t>361055; 427867</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>375816; 450065</t>
+          <t>379427; 448760</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>170573; 226685</t>
+          <t>192441; 243013</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>627326</t>
+          <t>674690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1504415</t>
+          <t>1577856</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>612171; 697989</t>
+          <t>611485; 703972</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>727203; 828792</t>
+          <t>725595; 827005</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>800313; 903042</t>
+          <t>809102; 909277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>484416; 689975</t>
+          <t>630080; 729958</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>997932; 1106023</t>
+          <t>994407; 1100709</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1099846; 1216422</t>
+          <t>1100203; 1213471</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1102313; 1215256</t>
+          <t>1101236; 1214739</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>733326; 1037066</t>
+          <t>858427; 950215</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1629141; 1779363</t>
+          <t>1634748; 1781557</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1855084; 2013227</t>
+          <t>1853305; 2003351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1939272; 2093439</t>
+          <t>1945114; 2092981</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1321708; 1685446</t>
+          <t>1515139; 1650392</t>
         </is>
       </c>
     </row>
